--- a/data/output/2025/evaluasi_92.xlsx
+++ b/data/output/2025/evaluasi_92.xlsx
@@ -2829,7 +2829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3155,18 +3155,410 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>35.5924847421634</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.795208935048851</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1034946755729</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.987695213565141</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-3.07009809637278</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.756756187615132</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.3020639190364129</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.9309666485206739</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8.340715917886122</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7.226742732384955</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.28666642488388</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7.55224108852688</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>7.967879709251442</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8.852578429334454</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9201</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Raja Ampat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>-5.082320066111569</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3183,7 +3575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3383,6 +3775,202 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>24.79217842858555</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.821179177924207</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-21.14525265512648</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.842089852809672</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-10.45540986378028</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.5042360250811374</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9203</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3.016573163605889</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3905,6 +4493,202 @@
       <c r="F18" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>20.34558190355737</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.638035344063248</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-22.58429932730777</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.05883927343034731</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-10.08559496116541</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.5422238796678023</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9204</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Maybrat</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2.842231732719682</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3919,7 +4703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4175,6 +4959,174 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>22.83024739471168</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.821798322726081</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-21.65106405528821</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.156620957769806</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-9.255685964575735</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9205</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Tambrauw</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.534893957120458</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4189,7 +5141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4417,6 +5369,146 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>20.55878650139567</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.6259739445925</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-16.31440568673032</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-6.868782268620823</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9271</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Sorong</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.079616198792309</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4431,7 +5523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4578,6 +5670,146 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>23.53755696152495</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.909447495941317</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-17.85988070774121</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-8.473874633290988</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sorong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.648590497640853</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
